--- a/artfynd/A 16684-2026 artfynd.xlsx
+++ b/artfynd/A 16684-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114588442</v>
+        <v>114588427</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582276</v>
+        <v>582394</v>
       </c>
       <c r="R2" t="n">
-        <v>6622779</v>
+        <v>6622466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114588441</v>
+        <v>114588439</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582265</v>
+        <v>582401</v>
       </c>
       <c r="R3" t="n">
-        <v>6622809</v>
+        <v>6622733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114588439</v>
+        <v>114588441</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582401</v>
+        <v>582265</v>
       </c>
       <c r="R4" t="n">
-        <v>6622733</v>
+        <v>6622809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114588448</v>
+        <v>114588442</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582375</v>
+        <v>582276</v>
       </c>
       <c r="R5" t="n">
-        <v>6622522</v>
+        <v>6622779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114588427</v>
+        <v>114588443</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582394</v>
+        <v>582210</v>
       </c>
       <c r="R6" t="n">
-        <v>6622466</v>
+        <v>6622833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114588443</v>
+        <v>114588444</v>
       </c>
       <c r="B7" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582210</v>
+        <v>582227</v>
       </c>
       <c r="R7" t="n">
-        <v>6622833</v>
+        <v>6622861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,50 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114588444</v>
+        <v>114588448</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582227</v>
+        <v>582375</v>
       </c>
       <c r="R8" t="n">
-        <v>6622861</v>
+        <v>6622522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,12 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,135 +1355,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115031183</v>
-      </c>
-      <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Skultuna, ca 1,8 km NO om Bentler Auminium (knärot), Vstm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>582375</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6622521</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Västerås</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Haraker</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>U-Väs-1506</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-11-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>inv. bliv. ledning Munga - Hallstahammar</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16684-2026 artfynd.xlsx
+++ b/artfynd/A 16684-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588442</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588443</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,8 +1390,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>